--- a/Data/EC/NIT-9006316982.xlsx
+++ b/Data/EC/NIT-9006316982.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E5D1567-196D-4354-BC7A-140CAF246AB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1055903F-62E1-483B-875C-5D9F73CDD906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8119424D-3D12-4D57-A945-63A960BEA1B3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{8C2A5B63-803D-4F9A-A351-528E589EC8BC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -71,163 +71,190 @@
     <t>CAMILO JOSE GARAY RANGEL</t>
   </si>
   <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
   </si>
   <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
+    <t>71480129</t>
+  </si>
+  <si>
+    <t>OMAR EVELIO LOPEZ MUÑOZ</t>
   </si>
   <si>
     <t>98472811</t>
@@ -240,33 +267,6 @@
   </si>
   <si>
     <t>WILMER ELIAS SALAZAR ZULUAGA</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>71480129</t>
-  </si>
-  <si>
-    <t>OMAR EVELIO LOPEZ MUÑOZ</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -365,9 +365,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -380,7 +378,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -580,23 +580,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -624,10 +624,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -665,22 +665,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1A3225FF-3D17-C62E-715F-22DFBA180D78}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D53E9C2-208F-1F45-F734-572CE3422548}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -702,7 +702,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1031,23 +1031,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5420F41-08AA-4EC3-8DFB-5F57274431C9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72A34F67-C847-4DA3-B0FB-64474F25B0EA}">
   <dimension ref="B2:J103"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="33" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
@@ -1060,7 +1060,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1071,7 +1071,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1082,7 +1082,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1093,8 +1093,8 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>78</v>
       </c>
@@ -1109,8 +1109,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1125,8 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
         <v>79</v>
       </c>
@@ -1141,8 +1141,8 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
         <v>80</v>
       </c>
@@ -1161,7 +1161,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1204,7 +1204,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>25774</v>
+        <v>21874</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1213,7 +1213,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1236,7 +1236,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1259,7 +1259,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1273,7 +1273,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1282,7 +1282,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1296,7 +1296,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1305,7 +1305,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1319,7 +1319,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1328,7 +1328,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1351,7 +1351,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1365,7 +1365,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1374,7 +1374,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1388,7 +1388,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1397,7 +1397,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1411,7 +1411,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1420,7 +1420,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1434,7 +1434,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1443,7 +1443,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1457,7 +1457,7 @@
         <v>22</v>
       </c>
       <c r="F27" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1466,7 +1466,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1480,7 +1480,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1489,7 +1489,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1503,7 +1503,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1512,7 +1512,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1535,7 +1535,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1549,7 +1549,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1558,7 +1558,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1572,7 +1572,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1581,7 +1581,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1595,7 +1595,7 @@
         <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1604,7 +1604,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1618,7 +1618,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G34" s="18">
         <v>781242</v>
@@ -1627,7 +1627,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1641,7 +1641,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1650,7 +1650,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1664,7 +1664,7 @@
         <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1673,7 +1673,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1687,7 +1687,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1696,7 +1696,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1710,7 +1710,7 @@
         <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1719,7 +1719,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1742,7 +1742,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1756,7 +1756,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1765,7 +1765,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1779,7 +1779,7 @@
         <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>25774</v>
+        <v>31249</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1788,7 +1788,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1811,7 +1811,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1834,7 +1834,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1857,7 +1857,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1880,7 +1880,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1903,7 +1903,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1926,7 +1926,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1949,7 +1949,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -1972,7 +1972,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -1986,7 +1986,7 @@
         <v>45</v>
       </c>
       <c r="F50" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G50" s="18">
         <v>781242</v>
@@ -1995,7 +1995,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>46</v>
       </c>
       <c r="F51" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G51" s="18">
         <v>781242</v>
@@ -2018,7 +2018,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2032,7 +2032,7 @@
         <v>47</v>
       </c>
       <c r="F52" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G52" s="18">
         <v>781242</v>
@@ -2041,7 +2041,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2055,7 +2055,7 @@
         <v>48</v>
       </c>
       <c r="F53" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G53" s="18">
         <v>781242</v>
@@ -2064,7 +2064,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2078,7 +2078,7 @@
         <v>49</v>
       </c>
       <c r="F54" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G54" s="18">
         <v>781242</v>
@@ -2087,7 +2087,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2101,7 +2101,7 @@
         <v>50</v>
       </c>
       <c r="F55" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G55" s="18">
         <v>781242</v>
@@ -2110,7 +2110,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2124,7 +2124,7 @@
         <v>51</v>
       </c>
       <c r="F56" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G56" s="18">
         <v>781242</v>
@@ -2133,7 +2133,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>52</v>
       </c>
       <c r="F57" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G57" s="18">
         <v>781242</v>
@@ -2156,7 +2156,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2170,7 +2170,7 @@
         <v>53</v>
       </c>
       <c r="F58" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G58" s="18">
         <v>781242</v>
@@ -2179,7 +2179,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2193,7 +2193,7 @@
         <v>54</v>
       </c>
       <c r="F59" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G59" s="18">
         <v>781242</v>
@@ -2202,7 +2202,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>55</v>
       </c>
       <c r="F60" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G60" s="18">
         <v>781242</v>
@@ -2225,7 +2225,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2239,7 +2239,7 @@
         <v>56</v>
       </c>
       <c r="F61" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G61" s="18">
         <v>781242</v>
@@ -2248,7 +2248,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2262,7 +2262,7 @@
         <v>57</v>
       </c>
       <c r="F62" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G62" s="18">
         <v>781242</v>
@@ -2271,7 +2271,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2285,7 +2285,7 @@
         <v>58</v>
       </c>
       <c r="F63" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G63" s="18">
         <v>781242</v>
@@ -2294,7 +2294,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>59</v>
       </c>
       <c r="F64" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G64" s="18">
         <v>781242</v>
@@ -2317,7 +2317,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2331,7 +2331,7 @@
         <v>60</v>
       </c>
       <c r="F65" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G65" s="18">
         <v>781242</v>
@@ -2340,7 +2340,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2354,7 +2354,7 @@
         <v>61</v>
       </c>
       <c r="F66" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G66" s="18">
         <v>781242</v>
@@ -2363,7 +2363,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2377,7 +2377,7 @@
         <v>62</v>
       </c>
       <c r="F67" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G67" s="18">
         <v>781242</v>
@@ -2386,7 +2386,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2400,7 +2400,7 @@
         <v>63</v>
       </c>
       <c r="F68" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G68" s="18">
         <v>781242</v>
@@ -2409,53 +2409,53 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D69" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E69" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D69" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>63</v>
-      </c>
       <c r="F69" s="18">
-        <v>35112</v>
+        <v>25774</v>
       </c>
       <c r="G69" s="18">
-        <v>877803</v>
+        <v>781242</v>
       </c>
       <c r="H69" s="19"/>
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="16" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="D70" s="17" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E70" s="16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F70" s="18">
-        <v>35112</v>
+        <v>25774</v>
       </c>
       <c r="G70" s="18">
-        <v>877803</v>
+        <v>781242</v>
       </c>
       <c r="H70" s="19"/>
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2466,10 +2466,10 @@
         <v>10</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="F71" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G71" s="18">
         <v>781242</v>
@@ -2478,53 +2478,53 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C72" s="16" t="s">
-        <v>64</v>
+        <v>9</v>
       </c>
       <c r="D72" s="17" t="s">
-        <v>65</v>
+        <v>10</v>
       </c>
       <c r="E72" s="16" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F72" s="18">
-        <v>35112</v>
+        <v>25774</v>
       </c>
       <c r="G72" s="18">
-        <v>877803</v>
+        <v>781242</v>
       </c>
       <c r="H72" s="19"/>
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C73" s="16" t="s">
-        <v>66</v>
+        <v>9</v>
       </c>
       <c r="D73" s="17" t="s">
-        <v>67</v>
+        <v>10</v>
       </c>
       <c r="E73" s="16" t="s">
         <v>68</v>
       </c>
       <c r="F73" s="18">
-        <v>35112</v>
+        <v>25774</v>
       </c>
       <c r="G73" s="18">
-        <v>877803</v>
+        <v>781242</v>
       </c>
       <c r="H73" s="19"/>
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2538,7 +2538,7 @@
         <v>69</v>
       </c>
       <c r="F74" s="18">
-        <v>31249</v>
+        <v>25774</v>
       </c>
       <c r="G74" s="18">
         <v>781242</v>
@@ -2547,44 +2547,44 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C75" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D75" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E75" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="D75" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="E75" s="16" t="s">
-        <v>69</v>
-      </c>
       <c r="F75" s="18">
-        <v>35112</v>
+        <v>25774</v>
       </c>
       <c r="G75" s="18">
-        <v>877803</v>
+        <v>781242</v>
       </c>
       <c r="H75" s="19"/>
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="16" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D76" s="17" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E76" s="16" t="s">
-        <v>69</v>
+        <v>11</v>
       </c>
       <c r="F76" s="18">
-        <v>35112</v>
+        <v>24578</v>
       </c>
       <c r="G76" s="18">
         <v>877803</v>
@@ -2593,18 +2593,18 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C77" s="16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D77" s="17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>69</v>
+        <v>12</v>
       </c>
       <c r="F77" s="18">
         <v>35112</v>
@@ -2616,41 +2616,41 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="16" t="s">
-        <v>9</v>
+        <v>71</v>
       </c>
       <c r="D78" s="17" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="E78" s="16" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="F78" s="18">
-        <v>31249</v>
+        <v>35112</v>
       </c>
       <c r="G78" s="18">
-        <v>781242</v>
+        <v>877803</v>
       </c>
       <c r="H78" s="19"/>
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="16" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D79" s="17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E79" s="16" t="s">
-        <v>72</v>
+        <v>14</v>
       </c>
       <c r="F79" s="18">
         <v>35112</v>
@@ -2662,18 +2662,18 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C80" s="16" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="D80" s="17" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="E80" s="16" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="F80" s="18">
         <v>35112</v>
@@ -2685,18 +2685,18 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C81" s="16" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="D81" s="17" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E81" s="16" t="s">
-        <v>72</v>
+        <v>16</v>
       </c>
       <c r="F81" s="18">
         <v>35112</v>
@@ -2708,41 +2708,41 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C82" s="16" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="D82" s="17" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="E82" s="16" t="s">
-        <v>73</v>
+        <v>11</v>
       </c>
       <c r="F82" s="18">
-        <v>31249</v>
+        <v>24578</v>
       </c>
       <c r="G82" s="18">
-        <v>781242</v>
+        <v>877803</v>
       </c>
       <c r="H82" s="19"/>
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C83" s="16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D83" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E83" s="16" t="s">
-        <v>73</v>
+        <v>12</v>
       </c>
       <c r="F83" s="18">
         <v>35112</v>
@@ -2754,18 +2754,18 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C84" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D84" s="17" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E84" s="16" t="s">
-        <v>73</v>
+        <v>13</v>
       </c>
       <c r="F84" s="18">
         <v>35112</v>
@@ -2777,18 +2777,18 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="16" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D85" s="17" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E85" s="16" t="s">
-        <v>73</v>
+        <v>14</v>
       </c>
       <c r="F85" s="18">
         <v>35112</v>
@@ -2800,41 +2800,41 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="16" t="s">
-        <v>9</v>
+        <v>73</v>
       </c>
       <c r="D86" s="17" t="s">
-        <v>10</v>
+        <v>74</v>
       </c>
       <c r="E86" s="16" t="s">
-        <v>74</v>
+        <v>15</v>
       </c>
       <c r="F86" s="18">
-        <v>31249</v>
+        <v>35112</v>
       </c>
       <c r="G86" s="18">
-        <v>781242</v>
+        <v>877803</v>
       </c>
       <c r="H86" s="19"/>
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C87" s="16" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D87" s="17" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="E87" s="16" t="s">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="F87" s="18">
         <v>35112</v>
@@ -2846,18 +2846,18 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C88" s="16" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D88" s="17" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="E88" s="16" t="s">
-        <v>74</v>
+        <v>17</v>
       </c>
       <c r="F88" s="18">
         <v>35112</v>
@@ -2869,18 +2869,18 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C89" s="16" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="D89" s="17" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="E89" s="16" t="s">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="F89" s="18">
         <v>35112</v>
@@ -2892,41 +2892,41 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C90" s="16" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D90" s="17" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="E90" s="16" t="s">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="F90" s="18">
-        <v>31249</v>
+        <v>24578</v>
       </c>
       <c r="G90" s="18">
-        <v>781242</v>
+        <v>877803</v>
       </c>
       <c r="H90" s="19"/>
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C91" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D91" s="17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E91" s="16" t="s">
-        <v>75</v>
+        <v>12</v>
       </c>
       <c r="F91" s="18">
         <v>35112</v>
@@ -2938,18 +2938,18 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="16" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D92" s="17" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E92" s="16" t="s">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="F92" s="18">
         <v>35112</v>
@@ -2961,18 +2961,18 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C93" s="16" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D93" s="17" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E93" s="16" t="s">
-        <v>75</v>
+        <v>14</v>
       </c>
       <c r="F93" s="18">
         <v>35112</v>
@@ -2984,44 +2984,44 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B94" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C94" s="16" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D94" s="17" t="s">
-        <v>10</v>
+        <v>76</v>
       </c>
       <c r="E94" s="16" t="s">
-        <v>76</v>
+        <v>15</v>
       </c>
       <c r="F94" s="18">
-        <v>21874</v>
+        <v>35112</v>
       </c>
       <c r="G94" s="18">
-        <v>781242</v>
+        <v>877803</v>
       </c>
       <c r="H94" s="19"/>
       <c r="I94" s="19"/>
       <c r="J94" s="20"/>
     </row>
-    <row r="95" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B95" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="16" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D95" s="17" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="E95" s="16" t="s">
-        <v>76</v>
+        <v>16</v>
       </c>
       <c r="F95" s="18">
-        <v>24578</v>
+        <v>35112</v>
       </c>
       <c r="G95" s="18">
         <v>877803</v>
@@ -3030,21 +3030,21 @@
       <c r="I95" s="19"/>
       <c r="J95" s="20"/>
     </row>
-    <row r="96" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="96" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B96" s="15" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="16" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="D96" s="17" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="E96" s="16" t="s">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="F96" s="18">
-        <v>24578</v>
+        <v>35112</v>
       </c>
       <c r="G96" s="18">
         <v>877803</v>
@@ -3053,21 +3053,21 @@
       <c r="I96" s="19"/>
       <c r="J96" s="20"/>
     </row>
-    <row r="97" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B97" s="21" t="s">
         <v>8</v>
       </c>
       <c r="C97" s="22" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D97" s="23" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="E97" s="22" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="F97" s="24">
-        <v>24578</v>
+        <v>35112</v>
       </c>
       <c r="G97" s="24">
         <v>877803</v>
@@ -3076,7 +3076,7 @@
       <c r="I97" s="25"/>
       <c r="J97" s="26"/>
     </row>
-    <row r="102" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B102" s="32" t="s">
         <v>86</v>
       </c>
@@ -3087,7 +3087,7 @@
       <c r="I102" s="1"/>
       <c r="J102" s="1"/>
     </row>
-    <row r="103" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B103" s="32" t="s">
         <v>85</v>
       </c>
